--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/YUKON_Datenbank/after_conversion_yukon_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/YUKON_Datenbank/after_conversion_yukon_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="120">
   <si>
     <t>location</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Database_number</t>
+  </si>
+  <si>
+    <t>Database_name</t>
   </si>
   <si>
     <t>Yukon</t>
@@ -734,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD89"/>
+  <dimension ref="A1:AE89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -761,9 +764,10 @@
     <col min="28" max="28" width="18.7109375" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" customWidth="1"/>
     <col min="30" max="30" width="17.7109375" customWidth="1"/>
+    <col min="31" max="31" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -854,13 +858,16 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30">
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2">
         <v>63.40501</v>
@@ -887,12 +894,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3">
         <v>59.4278</v>
@@ -931,12 +938,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4">
         <v>59.63029</v>
@@ -975,12 +982,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5">
         <v>60.38142</v>
@@ -1025,12 +1032,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6">
         <v>60.27582</v>
@@ -1075,12 +1082,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7">
         <v>60.00999</v>
@@ -1125,12 +1132,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8">
         <v>60.19948</v>
@@ -1175,12 +1182,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:31">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9">
         <v>61.42595</v>
@@ -1207,12 +1214,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:31">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10">
         <v>61.9415</v>
@@ -1239,12 +1246,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11">
         <v>61.7</v>
@@ -1271,12 +1278,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:31">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12">
         <v>62.343</v>
@@ -1291,12 +1298,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13">
         <v>62.817</v>
@@ -1323,12 +1330,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:31">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C14">
         <v>64.011</v>
@@ -1367,12 +1374,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:31">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15">
         <v>61.25238</v>
@@ -1399,12 +1406,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:31">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16">
         <v>62.37167</v>
@@ -1433,10 +1440,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17">
         <v>62.82168</v>
@@ -1465,10 +1472,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18">
         <v>62.6638</v>
@@ -1497,10 +1504,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19">
         <v>61.86137</v>
@@ -1541,10 +1548,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C20">
         <v>63.28318</v>
@@ -1561,10 +1568,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C21">
         <v>61.95491</v>
@@ -1593,10 +1600,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22">
         <v>60.8789</v>
@@ -1643,10 +1650,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C23">
         <v>60.76146</v>
@@ -1693,10 +1700,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C24">
         <v>60.75248</v>
@@ -1743,10 +1750,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C25">
         <v>60.78902</v>
@@ -1793,10 +1800,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C26">
         <v>60.78873</v>
@@ -1843,10 +1850,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C27">
         <v>60.74632</v>
@@ -1887,10 +1894,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C28">
         <v>63.06761</v>
@@ -1937,10 +1944,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C29">
         <v>63.70526</v>
@@ -1987,10 +1994,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C30">
         <v>60.90144</v>
@@ -2037,10 +2044,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C31">
         <v>64.55104</v>
@@ -2087,10 +2094,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C32">
         <v>64.60932</v>
@@ -2137,10 +2144,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C33">
         <v>60.19873</v>
@@ -2187,10 +2194,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C34">
         <v>60.19828</v>
@@ -2237,10 +2244,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C35">
         <v>60.15235</v>
@@ -2287,10 +2294,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C36">
         <v>61.66667</v>
@@ -2331,10 +2338,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C37">
         <v>57.40435</v>
@@ -2381,10 +2388,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C38">
         <v>57.01681</v>
@@ -2428,10 +2435,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C39">
         <v>57.71487</v>
@@ -2478,10 +2485,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B40" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C40">
         <v>57.77206</v>
@@ -2528,10 +2535,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C41">
         <v>60.915894</v>
@@ -2578,10 +2585,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C42">
         <v>59.98333</v>
@@ -2622,10 +2629,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B43" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C43">
         <v>59.96917</v>
@@ -2666,10 +2673,10 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B44" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C44">
         <v>55.9778245</v>
@@ -2686,10 +2693,10 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B45" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C45">
         <v>55.9299379</v>
@@ -2706,10 +2713,10 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B46" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C46">
         <v>55.865437</v>
@@ -2726,10 +2733,10 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C47">
         <v>56.2296634</v>
@@ -2746,10 +2753,10 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B48" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C48">
         <v>56.6755021</v>
@@ -2766,10 +2773,10 @@
     </row>
     <row r="49" spans="1:30">
       <c r="A49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B49" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C49">
         <v>61.95349</v>
@@ -2786,10 +2793,10 @@
     </row>
     <row r="50" spans="1:30">
       <c r="A50" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C50">
         <v>62.115</v>
@@ -2818,10 +2825,10 @@
     </row>
     <row r="51" spans="1:30">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B51" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C51">
         <v>61.4103</v>
@@ -2862,10 +2869,10 @@
     </row>
     <row r="52" spans="1:30">
       <c r="A52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B52" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C52">
         <v>59.472</v>
@@ -2882,10 +2889,10 @@
     </row>
     <row r="53" spans="1:30">
       <c r="A53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B53" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C53">
         <v>64.14593000000001</v>
@@ -2926,10 +2933,10 @@
     </row>
     <row r="54" spans="1:30">
       <c r="A54" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B54" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C54">
         <v>64.167</v>
@@ -2946,10 +2953,10 @@
     </row>
     <row r="55" spans="1:30">
       <c r="A55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B55" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C55">
         <v>64.009</v>
@@ -2990,10 +2997,10 @@
     </row>
     <row r="56" spans="1:30">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B56" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C56">
         <v>64.009</v>
@@ -3034,10 +3041,10 @@
     </row>
     <row r="57" spans="1:30">
       <c r="A57" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B57" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C57">
         <v>64.08333</v>
@@ -3078,10 +3085,10 @@
     </row>
     <row r="58" spans="1:30">
       <c r="A58" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B58" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C58">
         <v>59.96917</v>
@@ -3122,10 +3129,10 @@
     </row>
     <row r="59" spans="1:30">
       <c r="A59" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B59" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C59">
         <v>59.87721</v>
@@ -3166,10 +3173,10 @@
     </row>
     <row r="60" spans="1:30">
       <c r="A60" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B60" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C60">
         <v>59.40394</v>
@@ -3210,10 +3217,10 @@
     </row>
     <row r="61" spans="1:30">
       <c r="A61" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B61" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C61">
         <v>59.27227</v>
@@ -3230,10 +3237,10 @@
     </row>
     <row r="62" spans="1:30">
       <c r="A62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B62" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C62">
         <v>59.64472</v>
@@ -3250,10 +3257,10 @@
     </row>
     <row r="63" spans="1:30">
       <c r="A63" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B63" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C63">
         <v>59.50406</v>
@@ -3270,10 +3277,10 @@
     </row>
     <row r="64" spans="1:30">
       <c r="A64" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B64" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C64">
         <v>58.92503</v>
@@ -3290,10 +3297,10 @@
     </row>
     <row r="65" spans="1:30">
       <c r="A65" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B65" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C65">
         <v>59.4963</v>
@@ -3310,10 +3317,10 @@
     </row>
     <row r="66" spans="1:30">
       <c r="A66" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B66" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C66">
         <v>59.61295</v>
@@ -3330,10 +3337,10 @@
     </row>
     <row r="67" spans="1:30">
       <c r="A67" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B67" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C67">
         <v>62.00365</v>
@@ -3371,10 +3378,10 @@
     </row>
     <row r="68" spans="1:30">
       <c r="A68" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B68" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C68">
         <v>64.146</v>
@@ -3415,10 +3422,10 @@
     </row>
     <row r="69" spans="1:30">
       <c r="A69" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B69" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C69">
         <v>65.0309834</v>
@@ -3435,10 +3442,10 @@
     </row>
     <row r="70" spans="1:30">
       <c r="A70" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B70" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C70">
         <v>65.18466100000001</v>
@@ -3455,10 +3462,10 @@
     </row>
     <row r="71" spans="1:30">
       <c r="A71" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B71" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C71">
         <v>65.48945399999999</v>
@@ -3475,10 +3482,10 @@
     </row>
     <row r="72" spans="1:30">
       <c r="A72" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B72" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C72">
         <v>65.102092</v>
@@ -3495,10 +3502,10 @@
     </row>
     <row r="73" spans="1:30">
       <c r="A73" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B73" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C73">
         <v>64.488981</v>
@@ -3515,10 +3522,10 @@
     </row>
     <row r="74" spans="1:30">
       <c r="A74" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B74" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C74">
         <v>60.889151</v>
@@ -3535,10 +3542,10 @@
     </row>
     <row r="75" spans="1:30">
       <c r="A75" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B75" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C75">
         <v>58.665373</v>
@@ -3555,10 +3562,10 @@
     </row>
     <row r="76" spans="1:30">
       <c r="A76" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B76" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C76">
         <v>58.122279</v>
@@ -3575,10 +3582,10 @@
     </row>
     <row r="77" spans="1:30">
       <c r="A77" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B77" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C77">
         <v>58.005582</v>
@@ -3595,10 +3602,10 @@
     </row>
     <row r="78" spans="1:30">
       <c r="A78" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B78" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C78">
         <v>57.839992</v>
@@ -3615,10 +3622,10 @@
     </row>
     <row r="79" spans="1:30">
       <c r="A79" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B79" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C79">
         <v>57.769868</v>
@@ -3635,10 +3642,10 @@
     </row>
     <row r="80" spans="1:30">
       <c r="A80" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B80" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C80">
         <v>57.806075</v>
@@ -3655,10 +3662,10 @@
     </row>
     <row r="81" spans="1:30">
       <c r="A81" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B81" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C81">
         <v>57.778095</v>
@@ -3675,10 +3682,10 @@
     </row>
     <row r="82" spans="1:30">
       <c r="A82" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B82" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C82">
         <v>56.846531</v>
@@ -3695,10 +3702,10 @@
     </row>
     <row r="83" spans="1:30">
       <c r="A83" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B83" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C83">
         <v>56.718592</v>
@@ -3715,10 +3722,10 @@
     </row>
     <row r="84" spans="1:30">
       <c r="A84" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B84" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C84">
         <v>57.0896723</v>
@@ -3735,10 +3742,10 @@
     </row>
     <row r="85" spans="1:30">
       <c r="A85" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B85" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C85">
         <v>56.726836</v>
@@ -3755,10 +3762,10 @@
     </row>
     <row r="86" spans="1:30">
       <c r="A86" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B86" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C86">
         <v>56.6506976</v>
@@ -3775,10 +3782,10 @@
     </row>
     <row r="87" spans="1:30">
       <c r="A87" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B87" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C87">
         <v>56.7088271</v>
@@ -3795,10 +3802,10 @@
     </row>
     <row r="88" spans="1:30">
       <c r="A88" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B88" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C88">
         <v>56.4570945</v>
@@ -3815,10 +3822,10 @@
     </row>
     <row r="89" spans="1:30">
       <c r="A89" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B89" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C89">
         <v>56.1482276</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/YUKON_Datenbank/after_conversion_yukon_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/YUKON_Datenbank/after_conversion_yukon_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="121">
   <si>
     <t>location</t>
   </si>
@@ -374,6 +374,9 @@
   </si>
   <si>
     <t>Unuk River HS</t>
+  </si>
+  <si>
+    <t>Granite</t>
   </si>
 </sst>
 </file>
@@ -875,6 +878,9 @@
       <c r="D2">
         <v>-125.9557</v>
       </c>
+      <c r="F2" t="s">
+        <v>120</v>
+      </c>
       <c r="L2">
         <v>4.830264296907846</v>
       </c>
@@ -907,6 +913,9 @@
       <c r="D3">
         <v>-126.09892</v>
       </c>
+      <c r="F3" t="s">
+        <v>120</v>
+      </c>
       <c r="J3">
         <v>6.5</v>
       </c>
@@ -951,6 +960,9 @@
       <c r="D4">
         <v>-126.90672</v>
       </c>
+      <c r="F4" t="s">
+        <v>120</v>
+      </c>
       <c r="L4">
         <v>23.44470217941414</v>
       </c>
@@ -995,6 +1007,9 @@
       <c r="D5">
         <v>-125.56873</v>
       </c>
+      <c r="F5" t="s">
+        <v>120</v>
+      </c>
       <c r="I5">
         <v>667</v>
       </c>
@@ -1045,6 +1060,9 @@
       <c r="D6">
         <v>-125.64786</v>
       </c>
+      <c r="F6" t="s">
+        <v>120</v>
+      </c>
       <c r="I6">
         <v>423</v>
       </c>
@@ -1095,6 +1113,9 @@
       <c r="D7">
         <v>-125.74744</v>
       </c>
+      <c r="F7" t="s">
+        <v>120</v>
+      </c>
       <c r="I7">
         <v>488</v>
       </c>
@@ -1145,6 +1166,9 @@
       <c r="D8">
         <v>-125.78986</v>
       </c>
+      <c r="F8" t="s">
+        <v>120</v>
+      </c>
       <c r="I8">
         <v>367</v>
       </c>
@@ -1195,6 +1219,9 @@
       <c r="D9">
         <v>-126.57484</v>
       </c>
+      <c r="F9" t="s">
+        <v>120</v>
+      </c>
       <c r="L9">
         <v>4.292923000409463</v>
       </c>
@@ -1227,6 +1254,9 @@
       <c r="D10">
         <v>-127.17908</v>
       </c>
+      <c r="F10" t="s">
+        <v>120</v>
+      </c>
       <c r="L10">
         <v>6.920200282928578</v>
       </c>
@@ -1259,6 +1289,9 @@
       <c r="D11">
         <v>-127.283</v>
       </c>
+      <c r="F11" t="s">
+        <v>120</v>
+      </c>
       <c r="L11">
         <v>1.265778278320003</v>
       </c>
@@ -1291,6 +1324,9 @@
       <c r="D12">
         <v>-128.1591</v>
       </c>
+      <c r="F12" t="s">
+        <v>120</v>
+      </c>
       <c r="L12">
         <v>0</v>
       </c>
@@ -1311,6 +1347,9 @@
       <c r="D13">
         <v>-128.833</v>
       </c>
+      <c r="F13" t="s">
+        <v>120</v>
+      </c>
       <c r="L13">
         <v>2.549210062469401</v>
       </c>
@@ -1343,6 +1382,9 @@
       <c r="D14">
         <v>-129.00361</v>
       </c>
+      <c r="F14" t="s">
+        <v>120</v>
+      </c>
       <c r="J14">
         <v>7.88</v>
       </c>
@@ -1387,6 +1429,9 @@
       <c r="D15">
         <v>-124.05754</v>
       </c>
+      <c r="F15" t="s">
+        <v>120</v>
+      </c>
       <c r="L15">
         <v>75.59605438083913</v>
       </c>
@@ -1419,6 +1464,9 @@
       <c r="D16">
         <v>-128.67981</v>
       </c>
+      <c r="F16" t="s">
+        <v>120</v>
+      </c>
       <c r="L16">
         <v>2.997554591353343</v>
       </c>
@@ -1451,6 +1499,9 @@
       <c r="D17">
         <v>-128.1336</v>
       </c>
+      <c r="F17" t="s">
+        <v>120</v>
+      </c>
       <c r="L17">
         <v>8.606674644291481</v>
       </c>
@@ -1483,6 +1534,9 @@
       <c r="D18">
         <v>-127.91881</v>
       </c>
+      <c r="F18" t="s">
+        <v>120</v>
+      </c>
       <c r="L18">
         <v>5.234727582892625</v>
       </c>
@@ -1515,6 +1569,9 @@
       <c r="D19">
         <v>-129.66929</v>
       </c>
+      <c r="F19" t="s">
+        <v>120</v>
+      </c>
       <c r="J19">
         <v>7.3</v>
       </c>
@@ -1559,6 +1616,9 @@
       <c r="D20">
         <v>-130.22964</v>
       </c>
+      <c r="F20" t="s">
+        <v>120</v>
+      </c>
       <c r="L20">
         <v>0</v>
       </c>
@@ -1579,6 +1639,9 @@
       <c r="D21">
         <v>-128.20613</v>
       </c>
+      <c r="F21" t="s">
+        <v>120</v>
+      </c>
       <c r="L21">
         <v>2.31408230750115</v>
       </c>
@@ -1611,6 +1674,9 @@
       <c r="D22">
         <v>-135.36011</v>
       </c>
+      <c r="F22" t="s">
+        <v>120</v>
+      </c>
       <c r="I22">
         <v>2905</v>
       </c>
@@ -1661,6 +1727,9 @@
       <c r="D23">
         <v>-135.14582</v>
       </c>
+      <c r="F23" t="s">
+        <v>120</v>
+      </c>
       <c r="I23">
         <v>336</v>
       </c>
@@ -1711,6 +1780,9 @@
       <c r="D24">
         <v>-135.128</v>
       </c>
+      <c r="F24" t="s">
+        <v>120</v>
+      </c>
       <c r="I24">
         <v>347</v>
       </c>
@@ -1761,6 +1833,9 @@
       <c r="D25">
         <v>-135.20278</v>
       </c>
+      <c r="F25" t="s">
+        <v>120</v>
+      </c>
       <c r="I25">
         <v>360</v>
       </c>
@@ -1811,6 +1886,9 @@
       <c r="D26">
         <v>-135.20118</v>
       </c>
+      <c r="F26" t="s">
+        <v>120</v>
+      </c>
       <c r="I26">
         <v>404</v>
       </c>
@@ -1861,6 +1939,9 @@
       <c r="D27">
         <v>-135.10815</v>
       </c>
+      <c r="F27" t="s">
+        <v>120</v>
+      </c>
       <c r="L27">
         <v>3.714809613814364</v>
       </c>
@@ -1905,6 +1986,9 @@
       <c r="D28">
         <v>-135.71165</v>
       </c>
+      <c r="F28" t="s">
+        <v>120</v>
+      </c>
       <c r="I28">
         <v>268</v>
       </c>
@@ -1955,6 +2039,9 @@
       <c r="D29">
         <v>-137.31082</v>
       </c>
+      <c r="F29" t="s">
+        <v>120</v>
+      </c>
       <c r="I29">
         <v>441</v>
       </c>
@@ -2005,6 +2092,9 @@
       <c r="D30">
         <v>-137.96969</v>
       </c>
+      <c r="F30" t="s">
+        <v>120</v>
+      </c>
       <c r="I30">
         <v>660</v>
       </c>
@@ -2055,6 +2145,9 @@
       <c r="D31">
         <v>-134.70978</v>
       </c>
+      <c r="F31" t="s">
+        <v>120</v>
+      </c>
       <c r="I31">
         <v>390</v>
       </c>
@@ -2105,6 +2198,9 @@
       <c r="D32">
         <v>-135.00865</v>
       </c>
+      <c r="F32" t="s">
+        <v>120</v>
+      </c>
       <c r="I32">
         <v>207</v>
       </c>
@@ -2155,6 +2251,9 @@
       <c r="D33">
         <v>-125.51287</v>
       </c>
+      <c r="F33" t="s">
+        <v>120</v>
+      </c>
       <c r="I33">
         <v>554</v>
       </c>
@@ -2205,6 +2304,9 @@
       <c r="D34">
         <v>-125.52384</v>
       </c>
+      <c r="F34" t="s">
+        <v>120</v>
+      </c>
       <c r="I34">
         <v>538</v>
       </c>
@@ -2255,6 +2357,9 @@
       <c r="D35">
         <v>-127.43579</v>
       </c>
+      <c r="F35" t="s">
+        <v>120</v>
+      </c>
       <c r="I35">
         <v>531</v>
       </c>
@@ -2305,6 +2410,9 @@
       <c r="D36">
         <v>-127.58333</v>
       </c>
+      <c r="F36" t="s">
+        <v>120</v>
+      </c>
       <c r="J36">
         <v>7.06</v>
       </c>
@@ -2349,6 +2457,9 @@
       <c r="D37">
         <v>-130.91825</v>
       </c>
+      <c r="F37" t="s">
+        <v>120</v>
+      </c>
       <c r="I37">
         <v>2400</v>
       </c>
@@ -2399,6 +2510,9 @@
       <c r="D38">
         <v>-131.30861</v>
       </c>
+      <c r="F38" t="s">
+        <v>120</v>
+      </c>
       <c r="J38">
         <v>6.59</v>
       </c>
@@ -2446,6 +2560,9 @@
       <c r="D39">
         <v>-130.70947</v>
       </c>
+      <c r="F39" t="s">
+        <v>120</v>
+      </c>
       <c r="I39">
         <v>3000</v>
       </c>
@@ -2496,6 +2613,9 @@
       <c r="D40">
         <v>-130.74563</v>
       </c>
+      <c r="F40" t="s">
+        <v>120</v>
+      </c>
       <c r="I40">
         <v>2780</v>
       </c>
@@ -2546,6 +2666,9 @@
       <c r="D41">
         <v>-135.18883</v>
       </c>
+      <c r="F41" t="s">
+        <v>120</v>
+      </c>
       <c r="I41">
         <v>624</v>
       </c>
@@ -2596,6 +2719,9 @@
       <c r="D42">
         <v>-134.21667</v>
       </c>
+      <c r="F42" t="s">
+        <v>120</v>
+      </c>
       <c r="J42">
         <v>7.53</v>
       </c>
@@ -2640,6 +2766,9 @@
       <c r="D43">
         <v>-134.22623</v>
       </c>
+      <c r="F43" t="s">
+        <v>120</v>
+      </c>
       <c r="J43">
         <v>7.29</v>
       </c>
@@ -2684,6 +2813,9 @@
       <c r="D44">
         <v>-131.6640596</v>
       </c>
+      <c r="F44" t="s">
+        <v>120</v>
+      </c>
       <c r="L44">
         <v>0</v>
       </c>
@@ -2704,6 +2836,9 @@
       <c r="D45">
         <v>-131.568339</v>
       </c>
+      <c r="F45" t="s">
+        <v>120</v>
+      </c>
       <c r="L45">
         <v>0</v>
       </c>
@@ -2724,6 +2859,9 @@
       <c r="D46">
         <v>-131.0605</v>
       </c>
+      <c r="F46" t="s">
+        <v>120</v>
+      </c>
       <c r="L46">
         <v>0</v>
       </c>
@@ -2744,6 +2882,9 @@
       <c r="D47">
         <v>-131.4570819</v>
       </c>
+      <c r="F47" t="s">
+        <v>120</v>
+      </c>
       <c r="L47">
         <v>0</v>
       </c>
@@ -2764,6 +2905,9 @@
       <c r="D48">
         <v>131.8932711</v>
       </c>
+      <c r="F48" t="s">
+        <v>120</v>
+      </c>
       <c r="L48">
         <v>0</v>
       </c>
@@ -2784,6 +2928,9 @@
       <c r="D49">
         <v>-128.20347</v>
       </c>
+      <c r="F49" t="s">
+        <v>120</v>
+      </c>
       <c r="L49">
         <v>0</v>
       </c>
@@ -2804,6 +2951,9 @@
       <c r="D50">
         <v>-128.405</v>
       </c>
+      <c r="F50" t="s">
+        <v>120</v>
+      </c>
       <c r="L50">
         <v>1.057532220866887</v>
       </c>
@@ -2836,6 +2986,9 @@
       <c r="D51">
         <v>-127.88</v>
       </c>
+      <c r="F51" t="s">
+        <v>120</v>
+      </c>
       <c r="J51">
         <v>7.4</v>
       </c>
@@ -2880,6 +3033,9 @@
       <c r="D52">
         <v>-137.715</v>
       </c>
+      <c r="F52" t="s">
+        <v>120</v>
+      </c>
       <c r="L52">
         <v>0</v>
       </c>
@@ -2900,6 +3056,9 @@
       <c r="D53">
         <v>-128.45046</v>
       </c>
+      <c r="F53" t="s">
+        <v>120</v>
+      </c>
       <c r="J53">
         <v>7.4</v>
       </c>
@@ -2944,6 +3103,9 @@
       <c r="D54">
         <v>-128.25</v>
       </c>
+      <c r="F54" t="s">
+        <v>120</v>
+      </c>
       <c r="L54">
         <v>0</v>
       </c>
@@ -2964,6 +3126,9 @@
       <c r="D55">
         <v>-129.00417</v>
       </c>
+      <c r="F55" t="s">
+        <v>120</v>
+      </c>
       <c r="J55">
         <v>7.9</v>
       </c>
@@ -3008,6 +3173,9 @@
       <c r="D56">
         <v>-129.00861</v>
       </c>
+      <c r="F56" t="s">
+        <v>120</v>
+      </c>
       <c r="J56">
         <v>7.87</v>
       </c>
@@ -3052,6 +3220,9 @@
       <c r="D57">
         <v>-128.41667</v>
       </c>
+      <c r="F57" t="s">
+        <v>120</v>
+      </c>
       <c r="J57">
         <v>7.5</v>
       </c>
@@ -3096,6 +3267,9 @@
       <c r="D58">
         <v>-134.22623</v>
       </c>
+      <c r="F58" t="s">
+        <v>120</v>
+      </c>
       <c r="J58">
         <v>8.199999999999999</v>
       </c>
@@ -3140,6 +3314,9 @@
       <c r="D59">
         <v>-133.98356</v>
       </c>
+      <c r="F59" t="s">
+        <v>120</v>
+      </c>
       <c r="J59">
         <v>7.6</v>
       </c>
@@ -3184,6 +3361,9 @@
       <c r="D60">
         <v>-133.57545</v>
       </c>
+      <c r="F60" t="s">
+        <v>120</v>
+      </c>
       <c r="J60">
         <v>8.199999999999999</v>
       </c>
@@ -3228,6 +3408,9 @@
       <c r="D61">
         <v>-132.62351</v>
       </c>
+      <c r="F61" t="s">
+        <v>120</v>
+      </c>
       <c r="L61">
         <v>0</v>
       </c>
@@ -3248,6 +3431,9 @@
       <c r="D62">
         <v>-129.73254</v>
       </c>
+      <c r="F62" t="s">
+        <v>120</v>
+      </c>
       <c r="L62">
         <v>0</v>
       </c>
@@ -3268,6 +3454,9 @@
       <c r="D63">
         <v>-125.95633</v>
       </c>
+      <c r="F63" t="s">
+        <v>120</v>
+      </c>
       <c r="L63">
         <v>0</v>
       </c>
@@ -3288,6 +3477,9 @@
       <c r="D64">
         <v>-125.07669</v>
       </c>
+      <c r="F64" t="s">
+        <v>120</v>
+      </c>
       <c r="L64">
         <v>0</v>
       </c>
@@ -3308,6 +3500,9 @@
       <c r="D65">
         <v>-124.85186</v>
       </c>
+      <c r="F65" t="s">
+        <v>120</v>
+      </c>
       <c r="L65">
         <v>0</v>
       </c>
@@ -3328,6 +3523,9 @@
       <c r="D66">
         <v>-125.55107</v>
       </c>
+      <c r="F66" t="s">
+        <v>120</v>
+      </c>
       <c r="L66">
         <v>0</v>
       </c>
@@ -3348,6 +3546,9 @@
       <c r="D67">
         <v>-127.02467</v>
       </c>
+      <c r="F67" t="s">
+        <v>120</v>
+      </c>
       <c r="J67">
         <v>6.4</v>
       </c>
@@ -3389,6 +3590,9 @@
       <c r="D68">
         <v>-128.432</v>
       </c>
+      <c r="F68" t="s">
+        <v>120</v>
+      </c>
       <c r="J68">
         <v>7.3</v>
       </c>
@@ -3433,6 +3637,9 @@
       <c r="D69">
         <v>-146.0524335</v>
       </c>
+      <c r="F69" t="s">
+        <v>120</v>
+      </c>
       <c r="L69">
         <v>0</v>
       </c>
@@ -3453,6 +3660,9 @@
       <c r="D70">
         <v>-144.692004</v>
       </c>
+      <c r="F70" t="s">
+        <v>120</v>
+      </c>
       <c r="L70">
         <v>0</v>
       </c>
@@ -3473,6 +3683,9 @@
       <c r="D71">
         <v>-144.622314</v>
       </c>
+      <c r="F71" t="s">
+        <v>120</v>
+      </c>
       <c r="L71">
         <v>0</v>
       </c>
@@ -3493,6 +3706,9 @@
       <c r="D72">
         <v>-142.732627</v>
       </c>
+      <c r="F72" t="s">
+        <v>120</v>
+      </c>
       <c r="L72">
         <v>0</v>
       </c>
@@ -3513,6 +3729,9 @@
       <c r="D73">
         <v>-143.081535</v>
       </c>
+      <c r="F73" t="s">
+        <v>120</v>
+      </c>
       <c r="L73">
         <v>0</v>
       </c>
@@ -3533,6 +3752,9 @@
       <c r="D74">
         <v>-142.289668</v>
       </c>
+      <c r="F74" t="s">
+        <v>120</v>
+      </c>
       <c r="L74">
         <v>0</v>
       </c>
@@ -3553,6 +3775,9 @@
       <c r="D75">
         <v>-137.488566</v>
       </c>
+      <c r="F75" t="s">
+        <v>120</v>
+      </c>
       <c r="L75">
         <v>0</v>
       </c>
@@ -3573,6 +3798,9 @@
       <c r="D76">
         <v>-135.892103</v>
       </c>
+      <c r="F76" t="s">
+        <v>120</v>
+      </c>
       <c r="L76">
         <v>0</v>
       </c>
@@ -3593,6 +3821,9 @@
       <c r="D77">
         <v>-135.926934</v>
       </c>
+      <c r="F77" t="s">
+        <v>120</v>
+      </c>
       <c r="L77">
         <v>0</v>
       </c>
@@ -3613,6 +3844,9 @@
       <c r="D78">
         <v>-136.035412</v>
       </c>
+      <c r="F78" t="s">
+        <v>120</v>
+      </c>
       <c r="L78">
         <v>0</v>
       </c>
@@ -3633,6 +3867,9 @@
       <c r="D79">
         <v>-135.845988</v>
       </c>
+      <c r="F79" t="s">
+        <v>120</v>
+      </c>
       <c r="L79">
         <v>0</v>
       </c>
@@ -3653,6 +3890,9 @@
       <c r="D80">
         <v>-136.338884</v>
       </c>
+      <c r="F80" t="s">
+        <v>120</v>
+      </c>
       <c r="L80">
         <v>0</v>
       </c>
@@ -3673,6 +3913,9 @@
       <c r="D81">
         <v>-135.219618</v>
       </c>
+      <c r="F81" t="s">
+        <v>120</v>
+      </c>
       <c r="L81">
         <v>0</v>
       </c>
@@ -3693,6 +3936,9 @@
       <c r="D82">
         <v>-135.379772</v>
       </c>
+      <c r="F82" t="s">
+        <v>120</v>
+      </c>
       <c r="L82">
         <v>0</v>
       </c>
@@ -3713,6 +3959,9 @@
       <c r="D83">
         <v>-134.714728</v>
       </c>
+      <c r="F83" t="s">
+        <v>120</v>
+      </c>
       <c r="L83">
         <v>0</v>
       </c>
@@ -3733,6 +3982,9 @@
       <c r="D84">
         <v>-134.8305897</v>
       </c>
+      <c r="F84" t="s">
+        <v>120</v>
+      </c>
       <c r="L84">
         <v>0</v>
       </c>
@@ -3753,6 +4005,9 @@
       <c r="D85">
         <v>-132.05231</v>
       </c>
+      <c r="F85" t="s">
+        <v>120</v>
+      </c>
       <c r="L85">
         <v>0</v>
       </c>
@@ -3773,6 +4028,9 @@
       <c r="D86">
         <v>-132.2534895</v>
       </c>
+      <c r="F86" t="s">
+        <v>120</v>
+      </c>
       <c r="L86">
         <v>0</v>
       </c>
@@ -3793,6 +4051,9 @@
       <c r="D87">
         <v>-132.1978004</v>
       </c>
+      <c r="F87" t="s">
+        <v>120</v>
+      </c>
       <c r="L87">
         <v>0</v>
       </c>
@@ -3813,6 +4074,9 @@
       <c r="D88">
         <v>-132.6023179</v>
       </c>
+      <c r="F88" t="s">
+        <v>120</v>
+      </c>
       <c r="L88">
         <v>0</v>
       </c>
@@ -3832,6 +4096,9 @@
       </c>
       <c r="D89">
         <v>-130.9767313</v>
+      </c>
+      <c r="F89" t="s">
+        <v>120</v>
       </c>
       <c r="L89">
         <v>0</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/YUKON_Datenbank/after_conversion_yukon_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/YUKON_Datenbank/after_conversion_yukon_mapped_readable.xlsx
@@ -881,6 +881,9 @@
       <c r="F2" t="s">
         <v>120</v>
       </c>
+      <c r="H2">
+        <v>54</v>
+      </c>
       <c r="L2">
         <v>4.830264296907846</v>
       </c>
@@ -916,6 +919,9 @@
       <c r="F3" t="s">
         <v>120</v>
       </c>
+      <c r="H3">
+        <v>52</v>
+      </c>
       <c r="J3">
         <v>6.5</v>
       </c>
@@ -963,6 +969,9 @@
       <c r="F4" t="s">
         <v>120</v>
       </c>
+      <c r="H4">
+        <v>48</v>
+      </c>
       <c r="L4">
         <v>23.44470217941414</v>
       </c>
@@ -1010,6 +1019,9 @@
       <c r="F5" t="s">
         <v>120</v>
       </c>
+      <c r="H5">
+        <v>54.5</v>
+      </c>
       <c r="I5">
         <v>667</v>
       </c>
@@ -1063,6 +1075,9 @@
       <c r="F6" t="s">
         <v>120</v>
       </c>
+      <c r="H6">
+        <v>15</v>
+      </c>
       <c r="I6">
         <v>423</v>
       </c>
@@ -1116,6 +1131,9 @@
       <c r="F7" t="s">
         <v>120</v>
       </c>
+      <c r="H7">
+        <v>25.3</v>
+      </c>
       <c r="I7">
         <v>488</v>
       </c>
@@ -1169,6 +1187,9 @@
       <c r="F8" t="s">
         <v>120</v>
       </c>
+      <c r="H8">
+        <v>29.2</v>
+      </c>
       <c r="I8">
         <v>367</v>
       </c>
@@ -1222,6 +1243,9 @@
       <c r="F9" t="s">
         <v>120</v>
       </c>
+      <c r="H9">
+        <v>29</v>
+      </c>
       <c r="L9">
         <v>4.292923000409463</v>
       </c>
@@ -1257,6 +1281,9 @@
       <c r="F10" t="s">
         <v>120</v>
       </c>
+      <c r="H10">
+        <v>21</v>
+      </c>
       <c r="L10">
         <v>6.920200282928578</v>
       </c>
@@ -1292,6 +1319,9 @@
       <c r="F11" t="s">
         <v>120</v>
       </c>
+      <c r="H11">
+        <v>47</v>
+      </c>
       <c r="L11">
         <v>1.265778278320003</v>
       </c>
@@ -1327,6 +1357,9 @@
       <c r="F12" t="s">
         <v>120</v>
       </c>
+      <c r="H12">
+        <v>40</v>
+      </c>
       <c r="L12">
         <v>0</v>
       </c>
@@ -1350,6 +1383,9 @@
       <c r="F13" t="s">
         <v>120</v>
       </c>
+      <c r="H13">
+        <v>64</v>
+      </c>
       <c r="L13">
         <v>2.549210062469401</v>
       </c>
@@ -1385,6 +1421,9 @@
       <c r="F14" t="s">
         <v>120</v>
       </c>
+      <c r="H14">
+        <v>8.5</v>
+      </c>
       <c r="J14">
         <v>7.88</v>
       </c>
@@ -1432,6 +1471,9 @@
       <c r="F15" t="s">
         <v>120</v>
       </c>
+      <c r="H15">
+        <v>37</v>
+      </c>
       <c r="L15">
         <v>75.59605438083913</v>
       </c>
@@ -1467,6 +1509,9 @@
       <c r="F16" t="s">
         <v>120</v>
       </c>
+      <c r="H16">
+        <v>58</v>
+      </c>
       <c r="L16">
         <v>2.997554591353343</v>
       </c>
@@ -1502,6 +1547,9 @@
       <c r="F17" t="s">
         <v>120</v>
       </c>
+      <c r="H17">
+        <v>45</v>
+      </c>
       <c r="L17">
         <v>8.606674644291481</v>
       </c>
@@ -1537,6 +1585,9 @@
       <c r="F18" t="s">
         <v>120</v>
       </c>
+      <c r="H18">
+        <v>44</v>
+      </c>
       <c r="L18">
         <v>5.234727582892625</v>
       </c>
@@ -1572,6 +1623,9 @@
       <c r="F19" t="s">
         <v>120</v>
       </c>
+      <c r="H19">
+        <v>16</v>
+      </c>
       <c r="J19">
         <v>7.3</v>
       </c>
@@ -1619,6 +1673,9 @@
       <c r="F20" t="s">
         <v>120</v>
       </c>
+      <c r="H20">
+        <v>33</v>
+      </c>
       <c r="L20">
         <v>0</v>
       </c>
@@ -1642,6 +1699,9 @@
       <c r="F21" t="s">
         <v>120</v>
       </c>
+      <c r="H21">
+        <v>41</v>
+      </c>
       <c r="L21">
         <v>2.31408230750115</v>
       </c>
@@ -1677,6 +1737,9 @@
       <c r="F22" t="s">
         <v>120</v>
       </c>
+      <c r="H22">
+        <v>47</v>
+      </c>
       <c r="I22">
         <v>2905</v>
       </c>
@@ -1730,6 +1793,9 @@
       <c r="F23" t="s">
         <v>120</v>
       </c>
+      <c r="H23">
+        <v>12.7</v>
+      </c>
       <c r="I23">
         <v>336</v>
       </c>
@@ -1783,6 +1849,9 @@
       <c r="F24" t="s">
         <v>120</v>
       </c>
+      <c r="H24">
+        <v>18.5</v>
+      </c>
       <c r="I24">
         <v>347</v>
       </c>
@@ -1836,6 +1905,9 @@
       <c r="F25" t="s">
         <v>120</v>
       </c>
+      <c r="H25">
+        <v>15.8</v>
+      </c>
       <c r="I25">
         <v>360</v>
       </c>
@@ -1889,6 +1961,9 @@
       <c r="F26" t="s">
         <v>120</v>
       </c>
+      <c r="H26">
+        <v>12</v>
+      </c>
       <c r="I26">
         <v>404</v>
       </c>
@@ -1989,6 +2064,9 @@
       <c r="F28" t="s">
         <v>120</v>
       </c>
+      <c r="H28">
+        <v>54.5</v>
+      </c>
       <c r="I28">
         <v>268</v>
       </c>
@@ -2042,6 +2120,9 @@
       <c r="F29" t="s">
         <v>120</v>
       </c>
+      <c r="H29">
+        <v>25.1</v>
+      </c>
       <c r="I29">
         <v>441</v>
       </c>
@@ -2095,6 +2176,9 @@
       <c r="F30" t="s">
         <v>120</v>
       </c>
+      <c r="H30">
+        <v>17.7</v>
+      </c>
       <c r="I30">
         <v>660</v>
       </c>
@@ -2148,6 +2232,9 @@
       <c r="F31" t="s">
         <v>120</v>
       </c>
+      <c r="H31">
+        <v>45.6</v>
+      </c>
       <c r="I31">
         <v>390</v>
       </c>
@@ -2201,6 +2288,9 @@
       <c r="F32" t="s">
         <v>120</v>
       </c>
+      <c r="H32">
+        <v>10.2</v>
+      </c>
       <c r="I32">
         <v>207</v>
       </c>
@@ -2254,6 +2344,9 @@
       <c r="F33" t="s">
         <v>120</v>
       </c>
+      <c r="H33">
+        <v>53</v>
+      </c>
       <c r="I33">
         <v>554</v>
       </c>
@@ -2307,6 +2400,9 @@
       <c r="F34" t="s">
         <v>120</v>
       </c>
+      <c r="H34">
+        <v>43</v>
+      </c>
       <c r="I34">
         <v>538</v>
       </c>
@@ -2360,6 +2456,9 @@
       <c r="F35" t="s">
         <v>120</v>
       </c>
+      <c r="H35">
+        <v>13.2</v>
+      </c>
       <c r="I35">
         <v>531</v>
       </c>
@@ -2413,6 +2512,9 @@
       <c r="F36" t="s">
         <v>120</v>
       </c>
+      <c r="H36">
+        <v>11</v>
+      </c>
       <c r="J36">
         <v>7.06</v>
       </c>
@@ -2460,6 +2562,9 @@
       <c r="F37" t="s">
         <v>120</v>
       </c>
+      <c r="H37">
+        <v>42.5</v>
+      </c>
       <c r="I37">
         <v>2400</v>
       </c>
@@ -2513,6 +2618,9 @@
       <c r="F38" t="s">
         <v>120</v>
       </c>
+      <c r="H38">
+        <v>48.5</v>
+      </c>
       <c r="J38">
         <v>6.59</v>
       </c>
@@ -2563,6 +2671,9 @@
       <c r="F39" t="s">
         <v>120</v>
       </c>
+      <c r="H39">
+        <v>46</v>
+      </c>
       <c r="I39">
         <v>3000</v>
       </c>
@@ -2616,6 +2727,9 @@
       <c r="F40" t="s">
         <v>120</v>
       </c>
+      <c r="H40">
+        <v>36</v>
+      </c>
       <c r="I40">
         <v>2780</v>
       </c>
@@ -2669,6 +2783,9 @@
       <c r="F41" t="s">
         <v>120</v>
       </c>
+      <c r="H41">
+        <v>13.7</v>
+      </c>
       <c r="I41">
         <v>624</v>
       </c>
@@ -2722,6 +2839,9 @@
       <c r="F42" t="s">
         <v>120</v>
       </c>
+      <c r="H42">
+        <v>9.5</v>
+      </c>
       <c r="J42">
         <v>7.53</v>
       </c>
@@ -2769,6 +2889,9 @@
       <c r="F43" t="s">
         <v>120</v>
       </c>
+      <c r="H43">
+        <v>15</v>
+      </c>
       <c r="J43">
         <v>7.29</v>
       </c>
@@ -2816,6 +2939,9 @@
       <c r="F44" t="s">
         <v>120</v>
       </c>
+      <c r="H44">
+        <v>88.3</v>
+      </c>
       <c r="L44">
         <v>0</v>
       </c>
@@ -2839,6 +2965,9 @@
       <c r="F45" t="s">
         <v>120</v>
       </c>
+      <c r="H45">
+        <v>74</v>
+      </c>
       <c r="L45">
         <v>0</v>
       </c>
@@ -2885,6 +3014,9 @@
       <c r="F47" t="s">
         <v>120</v>
       </c>
+      <c r="H47">
+        <v>57</v>
+      </c>
       <c r="L47">
         <v>0</v>
       </c>
@@ -2908,6 +3040,9 @@
       <c r="F48" t="s">
         <v>120</v>
       </c>
+      <c r="H48">
+        <v>26</v>
+      </c>
       <c r="L48">
         <v>0</v>
       </c>
@@ -2931,6 +3066,9 @@
       <c r="F49" t="s">
         <v>120</v>
       </c>
+      <c r="H49">
+        <v>29</v>
+      </c>
       <c r="L49">
         <v>0</v>
       </c>
@@ -2954,6 +3092,9 @@
       <c r="F50" t="s">
         <v>120</v>
       </c>
+      <c r="H50">
+        <v>32</v>
+      </c>
       <c r="L50">
         <v>1.057532220866887</v>
       </c>
@@ -2989,6 +3130,9 @@
       <c r="F51" t="s">
         <v>120</v>
       </c>
+      <c r="H51">
+        <v>3</v>
+      </c>
       <c r="J51">
         <v>7.4</v>
       </c>
@@ -3059,6 +3203,9 @@
       <c r="F53" t="s">
         <v>120</v>
       </c>
+      <c r="H53">
+        <v>16</v>
+      </c>
       <c r="J53">
         <v>7.4</v>
       </c>
@@ -3129,6 +3276,9 @@
       <c r="F55" t="s">
         <v>120</v>
       </c>
+      <c r="H55">
+        <v>10</v>
+      </c>
       <c r="J55">
         <v>7.9</v>
       </c>
@@ -3176,6 +3326,9 @@
       <c r="F56" t="s">
         <v>120</v>
       </c>
+      <c r="H56">
+        <v>10</v>
+      </c>
       <c r="J56">
         <v>7.87</v>
       </c>
@@ -3223,6 +3376,9 @@
       <c r="F57" t="s">
         <v>120</v>
       </c>
+      <c r="H57">
+        <v>46</v>
+      </c>
       <c r="J57">
         <v>7.5</v>
       </c>
@@ -3270,6 +3426,9 @@
       <c r="F58" t="s">
         <v>120</v>
       </c>
+      <c r="H58">
+        <v>17</v>
+      </c>
       <c r="J58">
         <v>8.199999999999999</v>
       </c>
@@ -3317,6 +3476,9 @@
       <c r="F59" t="s">
         <v>120</v>
       </c>
+      <c r="H59">
+        <v>13</v>
+      </c>
       <c r="J59">
         <v>7.6</v>
       </c>
@@ -3364,6 +3526,9 @@
       <c r="F60" t="s">
         <v>120</v>
       </c>
+      <c r="H60">
+        <v>29</v>
+      </c>
       <c r="J60">
         <v>8.199999999999999</v>
       </c>
@@ -3457,6 +3622,9 @@
       <c r="F63" t="s">
         <v>120</v>
       </c>
+      <c r="H63">
+        <v>42</v>
+      </c>
       <c r="L63">
         <v>0</v>
       </c>
@@ -3526,6 +3694,9 @@
       <c r="F66" t="s">
         <v>120</v>
       </c>
+      <c r="H66">
+        <v>58</v>
+      </c>
       <c r="L66">
         <v>0</v>
       </c>
@@ -3549,6 +3720,9 @@
       <c r="F67" t="s">
         <v>120</v>
       </c>
+      <c r="H67">
+        <v>3</v>
+      </c>
       <c r="J67">
         <v>6.4</v>
       </c>
@@ -3593,6 +3767,9 @@
       <c r="F68" t="s">
         <v>120</v>
       </c>
+      <c r="H68">
+        <v>22</v>
+      </c>
       <c r="J68">
         <v>7.3</v>
       </c>
@@ -3640,6 +3817,9 @@
       <c r="F69" t="s">
         <v>120</v>
       </c>
+      <c r="H69">
+        <v>74</v>
+      </c>
       <c r="L69">
         <v>0</v>
       </c>
@@ -3663,6 +3843,9 @@
       <c r="F70" t="s">
         <v>120</v>
       </c>
+      <c r="H70">
+        <v>61</v>
+      </c>
       <c r="L70">
         <v>0</v>
       </c>
@@ -3686,6 +3869,9 @@
       <c r="F71" t="s">
         <v>120</v>
       </c>
+      <c r="H71">
+        <v>57.2</v>
+      </c>
       <c r="L71">
         <v>0</v>
       </c>
@@ -3801,6 +3987,9 @@
       <c r="F76" t="s">
         <v>120</v>
       </c>
+      <c r="H76">
+        <v>46</v>
+      </c>
       <c r="L76">
         <v>0</v>
       </c>
@@ -3824,6 +4013,9 @@
       <c r="F77" t="s">
         <v>120</v>
       </c>
+      <c r="H77">
+        <v>76</v>
+      </c>
       <c r="L77">
         <v>0</v>
       </c>
@@ -3870,6 +4062,9 @@
       <c r="F79" t="s">
         <v>120</v>
       </c>
+      <c r="H79">
+        <v>39</v>
+      </c>
       <c r="L79">
         <v>0</v>
       </c>
@@ -3893,6 +4088,9 @@
       <c r="F80" t="s">
         <v>120</v>
       </c>
+      <c r="H80">
+        <v>57.2</v>
+      </c>
       <c r="L80">
         <v>0</v>
       </c>
@@ -3916,6 +4114,9 @@
       <c r="F81" t="s">
         <v>120</v>
       </c>
+      <c r="H81">
+        <v>41.1</v>
+      </c>
       <c r="L81">
         <v>0</v>
       </c>
@@ -3939,6 +4140,9 @@
       <c r="F82" t="s">
         <v>120</v>
       </c>
+      <c r="H82">
+        <v>67.2</v>
+      </c>
       <c r="L82">
         <v>0</v>
       </c>
@@ -3985,6 +4189,9 @@
       <c r="F84" t="s">
         <v>120</v>
       </c>
+      <c r="H84">
+        <v>51.1</v>
+      </c>
       <c r="L84">
         <v>0</v>
       </c>
@@ -4008,6 +4215,9 @@
       <c r="F85" t="s">
         <v>120</v>
       </c>
+      <c r="H85">
+        <v>60</v>
+      </c>
       <c r="L85">
         <v>0</v>
       </c>
@@ -4053,6 +4263,9 @@
       </c>
       <c r="F87" t="s">
         <v>120</v>
+      </c>
+      <c r="H87">
+        <v>21</v>
       </c>
       <c r="L87">
         <v>0</v>
